--- a/data/availability/projects/ora/zed-west.xlsx
+++ b/data/availability/projects/ora/zed-west.xlsx
@@ -461,12 +461,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Zed West latest availability</t>
+          <t>Updated inventory for zed-west</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -577,22 +577,22 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Park Side Residence (PSR)</t>
+          <t>Park Side Residence</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Delivered / Off-Plan</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0% DP, installments over 10 years</t>
+          <t>0% Down payment, installments over 10 years</t>
         </is>
       </c>
     </row>
@@ -620,29 +620,29 @@
         <v>75</v>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Park Side Residence (PSR)</t>
+          <t>Park Side Residence</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Delivered / Off-Plan</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0% DP, installments over 10 years</t>
+          <t>0% Down payment, installments over 10 years</t>
         </is>
       </c>
     </row>
@@ -677,22 +677,22 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Park Side Residence (PSR)</t>
+          <t>Park Side Residence</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Delivered / Off-Plan</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0% DP, installments over 10 years</t>
+          <t>0% Down payment, installments over 10 years</t>
         </is>
       </c>
     </row>
@@ -727,22 +727,22 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Park Side Residence (PSR)</t>
+          <t>Park Side Residence</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Delivered / Off-Plan</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0% DP, installments over 10 years</t>
+          <t>0% Down payment, installments over 10 years</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Phase 3 Delivery</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Phase 3 Delivery</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Phase 3 Delivery</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,15 +995,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Park Side Residence (PSR)</t>
+          <t>Park Side Residence</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Studio 60 sqm</t>
+          <t>60 SQM Studio</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Delivered / Off-Plan</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0% DP, installments over 10 years</t>
+          <t>0% Down payment, installments over 10 years</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Park Side Residence (PSR)</t>
+          <t>Park Side Residence</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1072,25 +1072,25 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>74-76 sqm</t>
+          <t>74-76 SQM</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>10000000</v>
+        <v>10400000</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Delivered / Off-Plan</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0% DP, installments over 10 years</t>
+          <t>0% Down payment, installments over 10 years</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Park Side Residence (PSR)</t>
+          <t>Park Side Residence</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1133,12 +1133,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>106 sqm</t>
+          <t>106 SQM</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Delivered / Off-Plan</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0% DP, installments over 10 years</t>
+          <t>0% Down payment, installments over 10 years</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Park Side Residence (PSR)</t>
+          <t>Park Side Residence</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>171 sqm</t>
+          <t>171 SQM</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Delivered / Off-Plan</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0% DP, installments over 10 years</t>
+          <t>0% Down payment, installments over 10 years</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>85 sqm</t>
+          <t>85 SQM</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Phase 3 Delivery</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>125 sqm</t>
+          <t>125 SQM</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Phase 3 Delivery</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fully Finished</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1377,12 +1377,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>219 sqm</t>
+          <t>219 SQM</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Phase 3 Delivery</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">

--- a/data/availability/projects/ora/zed-west.xlsx
+++ b/data/availability/projects/ora/zed-west.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -654,7 +654,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -704,7 +704,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -804,7 +804,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -854,7 +854,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">

--- a/data/availability/projects/ora/zed-west.xlsx
+++ b/data/availability/projects/ora/zed-west.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -604,7 +604,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -654,7 +654,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -704,7 +704,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -804,7 +804,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -854,7 +854,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -985,7 +985,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
